--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d5dacaa8d86d805/Documents/Tadewos Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F091BF-9847-492E-9FF0-17C1F0F6CC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{08F091BF-9847-492E-9FF0-17C1F0F6CC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D19A7A9-61BE-408A-BA81-38D24820F9DD}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7C014026-0A71-4790-A2EC-DCA3AECDDF6B}"/>
   </bookViews>
@@ -39,9 +39,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Test</t>
+  </si>
+  <si>
+    <t>Test_1</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t>Testing</t>
   </si>
 </sst>
 </file>
@@ -413,15 +422,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF25A68B-07F6-4183-9563-6B4E62299BBF}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d5dacaa8d86d805/Documents/Tadewos Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{08F091BF-9847-492E-9FF0-17C1F0F6CC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D19A7A9-61BE-408A-BA81-38D24820F9DD}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{08F091BF-9847-492E-9FF0-17C1F0F6CC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40B25BCE-B495-40D4-8622-F33112A8E08B}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7C014026-0A71-4790-A2EC-DCA3AECDDF6B}"/>
   </bookViews>
@@ -47,10 +47,10 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>Test4</t>
+    <t>Testing</t>
   </si>
   <si>
-    <t>Testing</t>
+    <t>Test2</t>
   </si>
 </sst>
 </file>
@@ -103,6 +103,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -433,12 +437,12 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
